--- a/Folketællinger/FT_Brabrand_Sogn_sogn_1845.xlsx
+++ b/Folketællinger/FT_Brabrand_Sogn_sogn_1845.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15363" uniqueCount="1937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15432" uniqueCount="1950">
   <si>
     <t>Kilde</t>
   </si>
@@ -5302,6 +5302,9 @@
     <t>465.0</t>
   </si>
   <si>
+    <t>56.176509, 10.090299</t>
+  </si>
+  <si>
     <t>Simmon Jensen</t>
   </si>
   <si>
@@ -5332,6 +5335,10 @@
     <t>463.0</t>
   </si>
   <si>
+    <t xml:space="preserve">56.176509, 10.090299
+</t>
+  </si>
+  <si>
     <t>Johanne Christiane Jensen</t>
   </si>
   <si>
@@ -5353,6 +5360,9 @@
     <t>485.0</t>
   </si>
   <si>
+    <t>56.175302, 10.091715</t>
+  </si>
+  <si>
     <t>Jensine Kjerstine Nielsdatter</t>
   </si>
   <si>
@@ -5377,6 +5387,9 @@
     <t>hus, 17</t>
   </si>
   <si>
+    <t>56.175178, 10.090082</t>
+  </si>
+  <si>
     <t>husmand, lever af sin jordlod</t>
   </si>
   <si>
@@ -5395,6 +5408,9 @@
     <t>506.0</t>
   </si>
   <si>
+    <t>56.175089, 10.087357</t>
+  </si>
+  <si>
     <t>Jacob Hansen</t>
   </si>
   <si>
@@ -5479,6 +5495,9 @@
     <t>hus, 21</t>
   </si>
   <si>
+    <t>56.172690, 10.108641</t>
+  </si>
+  <si>
     <t>261636</t>
   </si>
   <si>
@@ -5551,6 +5570,9 @@
     <t>hus, 22</t>
   </si>
   <si>
+    <t>56.181504, 10.079715</t>
+  </si>
+  <si>
     <t>Rasmus Laursen</t>
   </si>
   <si>
@@ -5590,6 +5612,9 @@
     <t>hus, 25</t>
   </si>
   <si>
+    <t>56.180610, 10.129419</t>
+  </si>
+  <si>
     <t>261860</t>
   </si>
   <si>
@@ -5638,6 +5663,9 @@
     <t>615.0</t>
   </si>
   <si>
+    <t>56.165308, 10.081048</t>
+  </si>
+  <si>
     <t>Anne Jensdatter</t>
   </si>
   <si>
@@ -5677,6 +5705,9 @@
     <t>hus, 32</t>
   </si>
   <si>
+    <t>56.188057, 10.078239</t>
+  </si>
+  <si>
     <t>Jacobine Pedersen</t>
   </si>
   <si>
@@ -5719,6 +5750,9 @@
     <t>626.0</t>
   </si>
   <si>
+    <t>56.189132, 10.080857</t>
+  </si>
+  <si>
     <t>Karen Hansdatter</t>
   </si>
   <si>
@@ -5749,6 +5783,9 @@
     <t>hus, 35</t>
   </si>
   <si>
+    <t>56.164243, 10.079698</t>
+  </si>
+  <si>
     <t>Christine Pedersen</t>
   </si>
   <si>
@@ -5777,6 +5814,9 @@
   </si>
   <si>
     <t>skolen, 1</t>
+  </si>
+  <si>
+    <t>56.176218, 10.089234</t>
   </si>
   <si>
     <t>Johannes Hansen Thiesen</t>
@@ -52420,9 +52460,11 @@
       <c r="E618" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="F618" s="1"/>
+      <c r="F618" s="1" t="s">
+        <v>1762</v>
+      </c>
       <c r="G618" s="1" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="H618" s="1" t="s">
         <v>134</v>
@@ -52469,7 +52511,7 @@
         <v>135</v>
       </c>
       <c r="Z618" s="1" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="AA618" s="1" t="s">
         <v>35</v>
@@ -52483,7 +52525,7 @@
         <v>28</v>
       </c>
       <c r="B619" s="1" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="C619" s="1" t="s">
         <v>1241</v>
@@ -52494,7 +52536,9 @@
       <c r="E619" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="F619" s="1"/>
+      <c r="F619" s="1" t="s">
+        <v>1762</v>
+      </c>
       <c r="G619" s="1" t="s">
         <v>1073</v>
       </c>
@@ -52506,7 +52550,7 @@
       </c>
       <c r="J619" s="1"/>
       <c r="K619" s="1" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="L619" s="1" t="s">
         <v>61</v>
@@ -52543,7 +52587,7 @@
         <v>87</v>
       </c>
       <c r="Z619" s="1" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="AA619" s="1" t="s">
         <v>51</v>
@@ -52557,7 +52601,7 @@
         <v>28</v>
       </c>
       <c r="B620" s="1" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="C620" s="1" t="s">
         <v>1241</v>
@@ -52568,7 +52612,9 @@
       <c r="E620" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="F620" s="1"/>
+      <c r="F620" s="1" t="s">
+        <v>1762</v>
+      </c>
       <c r="G620" s="1" t="s">
         <v>748</v>
       </c>
@@ -52617,7 +52663,7 @@
         <v>105</v>
       </c>
       <c r="Z620" s="1" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="AA620" s="1" t="s">
         <v>35</v>
@@ -52631,7 +52677,7 @@
         <v>28</v>
       </c>
       <c r="B621" s="1" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="C621" s="1" t="s">
         <v>1241</v>
@@ -52642,9 +52688,11 @@
       <c r="E621" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="F621" s="1"/>
+      <c r="F621" s="1" t="s">
+        <v>1762</v>
+      </c>
       <c r="G621" s="1" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="H621" s="1" t="s">
         <v>351</v>
@@ -52654,7 +52702,7 @@
       </c>
       <c r="J621" s="1"/>
       <c r="K621" s="1" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="L621" s="1" t="s">
         <v>226</v>
@@ -52691,7 +52739,7 @@
         <v>351</v>
       </c>
       <c r="Z621" s="1" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="AA621" s="1" t="s">
         <v>51</v>
@@ -52705,7 +52753,7 @@
         <v>28</v>
       </c>
       <c r="B622" s="1" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="C622" s="1" t="s">
         <v>1241</v>
@@ -52716,9 +52764,11 @@
       <c r="E622" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="F622" s="1"/>
+      <c r="F622" s="1" t="s">
+        <v>1773</v>
+      </c>
       <c r="G622" s="1" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="H622" s="1" t="s">
         <v>56</v>
@@ -52765,7 +52815,7 @@
         <v>56</v>
       </c>
       <c r="Z622" s="1" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="AA622" s="1" t="s">
         <v>51</v>
@@ -52779,7 +52829,7 @@
         <v>28</v>
       </c>
       <c r="B623" s="1" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="C623" s="1" t="s">
         <v>1241</v>
@@ -52790,7 +52840,9 @@
       <c r="E623" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="F623" s="1"/>
+      <c r="F623" s="1" t="s">
+        <v>1762</v>
+      </c>
       <c r="G623" s="1" t="s">
         <v>1062</v>
       </c>
@@ -52802,15 +52854,15 @@
       </c>
       <c r="J623" s="1"/>
       <c r="K623" s="1" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="L623" s="1" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="M623" s="1"/>
       <c r="N623" s="1"/>
       <c r="O623" s="1" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="P623" s="1"/>
       <c r="Q623" s="1" t="s">
@@ -52839,7 +52891,7 @@
         <v>201</v>
       </c>
       <c r="Z623" s="1" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="AA623" s="1" t="s">
         <v>51</v>
@@ -52853,7 +52905,7 @@
         <v>28</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="C624" s="1" t="s">
         <v>1241</v>
@@ -52864,7 +52916,9 @@
       <c r="E624" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="F624" s="1"/>
+      <c r="F624" s="1" t="s">
+        <v>1762</v>
+      </c>
       <c r="G624" s="1" t="s">
         <v>1315</v>
       </c>
@@ -52913,7 +52967,7 @@
         <v>123</v>
       </c>
       <c r="Z624" s="1" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="AA624" s="1" t="s">
         <v>35</v>
@@ -52927,7 +52981,7 @@
         <v>28</v>
       </c>
       <c r="B625" s="1" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="C625" s="1" t="s">
         <v>1241</v>
@@ -52938,9 +52992,11 @@
       <c r="E625" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="F625" s="1"/>
+      <c r="F625" s="1" t="s">
+        <v>1781</v>
+      </c>
       <c r="G625" s="1" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
       <c r="H625" s="1" t="s">
         <v>752</v>
@@ -52950,7 +53006,7 @@
       </c>
       <c r="J625" s="1"/>
       <c r="K625" s="1" t="s">
-        <v>1780</v>
+        <v>1783</v>
       </c>
       <c r="L625" s="1" t="s">
         <v>174</v>
@@ -52987,7 +53043,7 @@
         <v>377</v>
       </c>
       <c r="Z625" s="1" t="s">
-        <v>1781</v>
+        <v>1784</v>
       </c>
       <c r="AA625" s="1" t="s">
         <v>51</v>
@@ -53001,7 +53057,7 @@
         <v>28</v>
       </c>
       <c r="B626" s="1" t="s">
-        <v>1782</v>
+        <v>1785</v>
       </c>
       <c r="C626" s="1" t="s">
         <v>1241</v>
@@ -53012,7 +53068,9 @@
       <c r="E626" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="F626" s="1"/>
+      <c r="F626" s="1" t="s">
+        <v>1781</v>
+      </c>
       <c r="G626" s="1" t="s">
         <v>1423</v>
       </c>
@@ -53061,7 +53119,7 @@
         <v>100</v>
       </c>
       <c r="Z626" s="1" t="s">
-        <v>1781</v>
+        <v>1784</v>
       </c>
       <c r="AA626" s="1" t="s">
         <v>35</v>
@@ -53075,7 +53133,7 @@
         <v>28</v>
       </c>
       <c r="B627" s="1" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="C627" s="1" t="s">
         <v>1241</v>
@@ -53086,9 +53144,11 @@
       <c r="E627" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="F627" s="1"/>
+      <c r="F627" s="1" t="s">
+        <v>1781</v>
+      </c>
       <c r="G627" s="1" t="s">
-        <v>1784</v>
+        <v>1787</v>
       </c>
       <c r="H627" s="1" t="s">
         <v>285</v>
@@ -53135,7 +53195,7 @@
         <v>286</v>
       </c>
       <c r="Z627" s="1" t="s">
-        <v>1781</v>
+        <v>1784</v>
       </c>
       <c r="AA627" s="1" t="s">
         <v>51</v>
@@ -53149,7 +53209,7 @@
         <v>28</v>
       </c>
       <c r="B628" s="1" t="s">
-        <v>1785</v>
+        <v>1788</v>
       </c>
       <c r="C628" s="1" t="s">
         <v>1241</v>
@@ -53158,9 +53218,11 @@
         <v>31</v>
       </c>
       <c r="E628" s="1" t="s">
-        <v>1786</v>
-      </c>
-      <c r="F628" s="1"/>
+        <v>1789</v>
+      </c>
+      <c r="F628" s="1" t="s">
+        <v>1790</v>
+      </c>
       <c r="G628" s="1" t="s">
         <v>1073</v>
       </c>
@@ -53172,7 +53234,7 @@
       </c>
       <c r="J628" s="1"/>
       <c r="K628" s="1" t="s">
-        <v>1787</v>
+        <v>1791</v>
       </c>
       <c r="L628" s="1" t="s">
         <v>61</v>
@@ -53209,7 +53271,7 @@
         <v>536</v>
       </c>
       <c r="Z628" s="1" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
       <c r="AA628" s="1" t="s">
         <v>51</v>
@@ -53223,7 +53285,7 @@
         <v>28</v>
       </c>
       <c r="B629" s="1" t="s">
-        <v>1789</v>
+        <v>1793</v>
       </c>
       <c r="C629" s="1" t="s">
         <v>1241</v>
@@ -53232,11 +53294,13 @@
         <v>31</v>
       </c>
       <c r="E629" s="1" t="s">
-        <v>1786</v>
-      </c>
-      <c r="F629" s="1"/>
+        <v>1789</v>
+      </c>
+      <c r="F629" s="1" t="s">
+        <v>1790</v>
+      </c>
       <c r="G629" s="1" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
       <c r="H629" s="1" t="s">
         <v>402</v>
@@ -53283,7 +53347,7 @@
         <v>166</v>
       </c>
       <c r="Z629" s="1" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
       <c r="AA629" s="1" t="s">
         <v>35</v>
@@ -53297,7 +53361,7 @@
         <v>28</v>
       </c>
       <c r="B630" s="1" t="s">
-        <v>1791</v>
+        <v>1795</v>
       </c>
       <c r="C630" s="1" t="s">
         <v>1241</v>
@@ -53306,9 +53370,11 @@
         <v>31</v>
       </c>
       <c r="E630" s="1" t="s">
-        <v>1786</v>
-      </c>
-      <c r="F630" s="1"/>
+        <v>1789</v>
+      </c>
+      <c r="F630" s="1" t="s">
+        <v>1790</v>
+      </c>
       <c r="G630" s="1" t="s">
         <v>1468</v>
       </c>
@@ -53357,7 +53423,7 @@
         <v>377</v>
       </c>
       <c r="Z630" s="1" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
       <c r="AA630" s="1" t="s">
         <v>51</v>
@@ -53371,7 +53437,7 @@
         <v>28</v>
       </c>
       <c r="B631" s="1" t="s">
-        <v>1792</v>
+        <v>1796</v>
       </c>
       <c r="C631" s="1" t="s">
         <v>1241</v>
@@ -53382,9 +53448,11 @@
       <c r="E631" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F631" s="1"/>
+      <c r="F631" s="1" t="s">
+        <v>1797</v>
+      </c>
       <c r="G631" s="1" t="s">
-        <v>1793</v>
+        <v>1798</v>
       </c>
       <c r="H631" s="1" t="s">
         <v>121</v>
@@ -53431,7 +53499,7 @@
         <v>122</v>
       </c>
       <c r="Z631" s="1" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="AA631" s="1" t="s">
         <v>35</v>
@@ -53445,7 +53513,7 @@
         <v>28</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="C632" s="1" t="s">
         <v>1241</v>
@@ -53456,9 +53524,11 @@
       <c r="E632" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F632" s="1"/>
+      <c r="F632" s="1" t="s">
+        <v>1797</v>
+      </c>
       <c r="G632" s="1" t="s">
-        <v>1796</v>
+        <v>1801</v>
       </c>
       <c r="H632" s="1" t="s">
         <v>31</v>
@@ -53505,7 +53575,7 @@
         <v>179</v>
       </c>
       <c r="Z632" s="1" t="s">
-        <v>1797</v>
+        <v>1802</v>
       </c>
       <c r="AA632" s="1" t="s">
         <v>35</v>
@@ -53519,7 +53589,7 @@
         <v>28</v>
       </c>
       <c r="B633" s="1" t="s">
-        <v>1798</v>
+        <v>1803</v>
       </c>
       <c r="C633" s="1" t="s">
         <v>1241</v>
@@ -53530,7 +53600,9 @@
       <c r="E633" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F633" s="1"/>
+      <c r="F633" s="1" t="s">
+        <v>1797</v>
+      </c>
       <c r="G633" s="1" t="s">
         <v>315</v>
       </c>
@@ -53542,7 +53614,7 @@
       </c>
       <c r="J633" s="1"/>
       <c r="K633" s="1" t="s">
-        <v>1799</v>
+        <v>1804</v>
       </c>
       <c r="L633" s="1" t="s">
         <v>683</v>
@@ -53579,7 +53651,7 @@
         <v>697</v>
       </c>
       <c r="Z633" s="1" t="s">
-        <v>1800</v>
+        <v>1805</v>
       </c>
       <c r="AA633" s="1" t="s">
         <v>51</v>
@@ -53593,7 +53665,7 @@
         <v>28</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>1801</v>
+        <v>1806</v>
       </c>
       <c r="C634" s="1" t="s">
         <v>1241</v>
@@ -53604,7 +53676,9 @@
       <c r="E634" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F634" s="1"/>
+      <c r="F634" s="1" t="s">
+        <v>1797</v>
+      </c>
       <c r="G634" s="1" t="s">
         <v>885</v>
       </c>
@@ -53653,7 +53727,7 @@
         <v>179</v>
       </c>
       <c r="Z634" s="1" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="AA634" s="1" t="s">
         <v>35</v>
@@ -53667,7 +53741,7 @@
         <v>28</v>
       </c>
       <c r="B635" s="1" t="s">
-        <v>1802</v>
+        <v>1807</v>
       </c>
       <c r="C635" s="1" t="s">
         <v>1241</v>
@@ -53678,7 +53752,9 @@
       <c r="E635" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F635" s="1"/>
+      <c r="F635" s="1" t="s">
+        <v>1797</v>
+      </c>
       <c r="G635" s="1" t="s">
         <v>528</v>
       </c>
@@ -53727,7 +53803,7 @@
         <v>184</v>
       </c>
       <c r="Z635" s="1" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="AA635" s="1" t="s">
         <v>35</v>
@@ -53741,7 +53817,7 @@
         <v>28</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>1803</v>
+        <v>1808</v>
       </c>
       <c r="C636" s="1" t="s">
         <v>1241</v>
@@ -53752,9 +53828,11 @@
       <c r="E636" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F636" s="1"/>
+      <c r="F636" s="1" t="s">
+        <v>1797</v>
+      </c>
       <c r="G636" s="1" t="s">
-        <v>1804</v>
+        <v>1809</v>
       </c>
       <c r="H636" s="1" t="s">
         <v>74</v>
@@ -53801,7 +53879,7 @@
         <v>78</v>
       </c>
       <c r="Z636" s="1" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="AA636" s="1" t="s">
         <v>51</v>
@@ -53815,7 +53893,7 @@
         <v>28</v>
       </c>
       <c r="B637" s="1" t="s">
-        <v>1805</v>
+        <v>1810</v>
       </c>
       <c r="C637" s="1" t="s">
         <v>1241</v>
@@ -53826,9 +53904,11 @@
       <c r="E637" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F637" s="1"/>
+      <c r="F637" s="1" t="s">
+        <v>1797</v>
+      </c>
       <c r="G637" s="1" t="s">
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="H637" s="1" t="s">
         <v>153</v>
@@ -53838,7 +53918,7 @@
       </c>
       <c r="J637" s="1"/>
       <c r="K637" s="1" t="s">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="L637" s="1" t="s">
         <v>319</v>
@@ -53875,7 +53955,7 @@
         <v>87</v>
       </c>
       <c r="Z637" s="1" t="s">
-        <v>1797</v>
+        <v>1802</v>
       </c>
       <c r="AA637" s="1" t="s">
         <v>51</v>
@@ -53889,7 +53969,7 @@
         <v>28</v>
       </c>
       <c r="B638" s="1" t="s">
-        <v>1808</v>
+        <v>1813</v>
       </c>
       <c r="C638" s="1" t="s">
         <v>1241</v>
@@ -53900,9 +53980,11 @@
       <c r="E638" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F638" s="1"/>
+      <c r="F638" s="1" t="s">
+        <v>1797</v>
+      </c>
       <c r="G638" s="1" t="s">
-        <v>1809</v>
+        <v>1814</v>
       </c>
       <c r="H638" s="1" t="s">
         <v>103</v>
@@ -53949,7 +54031,7 @@
         <v>104</v>
       </c>
       <c r="Z638" s="1" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="AA638" s="1" t="s">
         <v>35</v>
@@ -53963,7 +54045,7 @@
         <v>28</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>1810</v>
+        <v>1815</v>
       </c>
       <c r="C639" s="1" t="s">
         <v>1241</v>
@@ -53974,9 +54056,11 @@
       <c r="E639" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F639" s="1"/>
+      <c r="F639" s="1" t="s">
+        <v>1797</v>
+      </c>
       <c r="G639" s="1" t="s">
-        <v>1811</v>
+        <v>1816</v>
       </c>
       <c r="H639" s="1" t="s">
         <v>275</v>
@@ -53986,7 +54070,7 @@
       </c>
       <c r="J639" s="1"/>
       <c r="K639" s="1" t="s">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="L639" s="1" t="s">
         <v>683</v>
@@ -54023,7 +54107,7 @@
         <v>278</v>
       </c>
       <c r="Z639" s="1" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="AA639" s="1" t="s">
         <v>51</v>
@@ -54037,7 +54121,7 @@
         <v>28</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>1812</v>
+        <v>1817</v>
       </c>
       <c r="C640" s="1" t="s">
         <v>1241</v>
@@ -54048,9 +54132,11 @@
       <c r="E640" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F640" s="1"/>
+      <c r="F640" s="1" t="s">
+        <v>1797</v>
+      </c>
       <c r="G640" s="1" t="s">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="H640" s="1" t="s">
         <v>50</v>
@@ -54097,7 +54183,7 @@
         <v>55</v>
       </c>
       <c r="Z640" s="1" t="s">
-        <v>1797</v>
+        <v>1802</v>
       </c>
       <c r="AA640" s="1" t="s">
         <v>51</v>
@@ -54111,7 +54197,7 @@
         <v>28</v>
       </c>
       <c r="B641" s="1" t="s">
-        <v>1814</v>
+        <v>1819</v>
       </c>
       <c r="C641" s="1" t="s">
         <v>1241</v>
@@ -54122,9 +54208,11 @@
       <c r="E641" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F641" s="1"/>
+      <c r="F641" s="1" t="s">
+        <v>1797</v>
+      </c>
       <c r="G641" s="1" t="s">
-        <v>1815</v>
+        <v>1820</v>
       </c>
       <c r="H641" s="1" t="s">
         <v>665</v>
@@ -54134,7 +54222,7 @@
       </c>
       <c r="J641" s="1"/>
       <c r="K641" s="1" t="s">
-        <v>1816</v>
+        <v>1821</v>
       </c>
       <c r="L641" s="1" t="s">
         <v>61</v>
@@ -54171,7 +54259,7 @@
         <v>665</v>
       </c>
       <c r="Z641" s="1" t="s">
-        <v>1800</v>
+        <v>1805</v>
       </c>
       <c r="AA641" s="1" t="s">
         <v>51</v>
@@ -54185,7 +54273,7 @@
         <v>28</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>1817</v>
+        <v>1822</v>
       </c>
       <c r="C642" s="1" t="s">
         <v>1241</v>
@@ -54196,9 +54284,11 @@
       <c r="E642" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="F642" s="1"/>
+      <c r="F642" s="1" t="s">
+        <v>1797</v>
+      </c>
       <c r="G642" s="1" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="H642" s="1" t="s">
         <v>70</v>
@@ -54245,7 +54335,7 @@
         <v>70</v>
       </c>
       <c r="Z642" s="1" t="s">
-        <v>1794</v>
+        <v>1799</v>
       </c>
       <c r="AA642" s="1" t="s">
         <v>35</v>
@@ -54259,7 +54349,7 @@
         <v>28</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>1819</v>
+        <v>1824</v>
       </c>
       <c r="C643" s="1" t="s">
         <v>1241</v>
@@ -54268,9 +54358,11 @@
         <v>178</v>
       </c>
       <c r="E643" s="1" t="s">
-        <v>1820</v>
-      </c>
-      <c r="F643" s="1"/>
+        <v>1825</v>
+      </c>
+      <c r="F643" s="1" t="s">
+        <v>1826</v>
+      </c>
       <c r="G643" s="1" t="s">
         <v>1580</v>
       </c>
@@ -54319,7 +54411,7 @@
         <v>123</v>
       </c>
       <c r="Z643" s="1" t="s">
-        <v>1821</v>
+        <v>1827</v>
       </c>
       <c r="AA643" s="1" t="s">
         <v>35</v>
@@ -54333,7 +54425,7 @@
         <v>28</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>1822</v>
+        <v>1828</v>
       </c>
       <c r="C644" s="1" t="s">
         <v>1241</v>
@@ -54342,11 +54434,13 @@
         <v>31</v>
       </c>
       <c r="E644" s="1" t="s">
-        <v>1820</v>
-      </c>
-      <c r="F644" s="1"/>
+        <v>1825</v>
+      </c>
+      <c r="F644" s="1" t="s">
+        <v>1826</v>
+      </c>
       <c r="G644" s="1" t="s">
-        <v>1823</v>
+        <v>1829</v>
       </c>
       <c r="H644" s="1" t="s">
         <v>121</v>
@@ -54393,7 +54487,7 @@
         <v>122</v>
       </c>
       <c r="Z644" s="1" t="s">
-        <v>1824</v>
+        <v>1830</v>
       </c>
       <c r="AA644" s="1" t="s">
         <v>35</v>
@@ -54407,7 +54501,7 @@
         <v>28</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>1825</v>
+        <v>1831</v>
       </c>
       <c r="C645" s="1" t="s">
         <v>1241</v>
@@ -54416,11 +54510,13 @@
         <v>31</v>
       </c>
       <c r="E645" s="1" t="s">
-        <v>1820</v>
-      </c>
-      <c r="F645" s="1"/>
+        <v>1825</v>
+      </c>
+      <c r="F645" s="1" t="s">
+        <v>1826</v>
+      </c>
       <c r="G645" s="1" t="s">
-        <v>1826</v>
+        <v>1832</v>
       </c>
       <c r="H645" s="1" t="s">
         <v>574</v>
@@ -54430,15 +54526,15 @@
       </c>
       <c r="J645" s="1"/>
       <c r="K645" s="1" t="s">
-        <v>1827</v>
+        <v>1833</v>
       </c>
       <c r="L645" s="1" t="s">
-        <v>1828</v>
+        <v>1834</v>
       </c>
       <c r="M645" s="1"/>
       <c r="N645" s="1"/>
       <c r="O645" s="1" t="s">
-        <v>1829</v>
+        <v>1835</v>
       </c>
       <c r="P645" s="1"/>
       <c r="Q645" s="1" t="s">
@@ -54467,7 +54563,7 @@
         <v>537</v>
       </c>
       <c r="Z645" s="1" t="s">
-        <v>1824</v>
+        <v>1830</v>
       </c>
       <c r="AA645" s="1" t="s">
         <v>51</v>
@@ -54481,7 +54577,7 @@
         <v>28</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>1830</v>
+        <v>1836</v>
       </c>
       <c r="C646" s="1" t="s">
         <v>1241</v>
@@ -54490,11 +54586,13 @@
         <v>31</v>
       </c>
       <c r="E646" s="1" t="s">
-        <v>1820</v>
-      </c>
-      <c r="F646" s="1"/>
+        <v>1825</v>
+      </c>
+      <c r="F646" s="1" t="s">
+        <v>1826</v>
+      </c>
       <c r="G646" s="1" t="s">
-        <v>1831</v>
+        <v>1837</v>
       </c>
       <c r="H646" s="1" t="s">
         <v>59</v>
@@ -54541,7 +54639,7 @@
         <v>64</v>
       </c>
       <c r="Z646" s="1" t="s">
-        <v>1824</v>
+        <v>1830</v>
       </c>
       <c r="AA646" s="1" t="s">
         <v>35</v>
@@ -54555,7 +54653,7 @@
         <v>28</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>1832</v>
+        <v>1838</v>
       </c>
       <c r="C647" s="1" t="s">
         <v>1241</v>
@@ -54564,11 +54662,13 @@
         <v>178</v>
       </c>
       <c r="E647" s="1" t="s">
-        <v>1820</v>
-      </c>
-      <c r="F647" s="1"/>
+        <v>1825</v>
+      </c>
+      <c r="F647" s="1" t="s">
+        <v>1826</v>
+      </c>
       <c r="G647" s="1" t="s">
-        <v>1833</v>
+        <v>1839</v>
       </c>
       <c r="H647" s="1" t="s">
         <v>402</v>
@@ -54578,7 +54678,7 @@
       </c>
       <c r="J647" s="1"/>
       <c r="K647" s="1" t="s">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="L647" s="1" t="s">
         <v>774</v>
@@ -54615,7 +54715,7 @@
         <v>166</v>
       </c>
       <c r="Z647" s="1" t="s">
-        <v>1821</v>
+        <v>1827</v>
       </c>
       <c r="AA647" s="1" t="s">
         <v>51</v>
@@ -54629,7 +54729,7 @@
         <v>28</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>1834</v>
+        <v>1840</v>
       </c>
       <c r="C648" s="1" t="s">
         <v>1241</v>
@@ -54638,11 +54738,13 @@
         <v>31</v>
       </c>
       <c r="E648" s="1" t="s">
-        <v>1820</v>
-      </c>
-      <c r="F648" s="1"/>
+        <v>1825</v>
+      </c>
+      <c r="F648" s="1" t="s">
+        <v>1826</v>
+      </c>
       <c r="G648" s="1" t="s">
-        <v>1835</v>
+        <v>1841</v>
       </c>
       <c r="H648" s="1" t="s">
         <v>316</v>
@@ -54689,7 +54791,7 @@
         <v>211</v>
       </c>
       <c r="Z648" s="1" t="s">
-        <v>1824</v>
+        <v>1830</v>
       </c>
       <c r="AA648" s="1" t="s">
         <v>51</v>
@@ -54703,7 +54805,7 @@
         <v>28</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>1836</v>
+        <v>1842</v>
       </c>
       <c r="C649" s="1" t="s">
         <v>1241</v>
@@ -54712,11 +54814,13 @@
         <v>121</v>
       </c>
       <c r="E649" s="1" t="s">
-        <v>1820</v>
-      </c>
-      <c r="F649" s="1"/>
+        <v>1825</v>
+      </c>
+      <c r="F649" s="1" t="s">
+        <v>1826</v>
+      </c>
       <c r="G649" s="1" t="s">
-        <v>1837</v>
+        <v>1843</v>
       </c>
       <c r="H649" s="1" t="s">
         <v>153</v>
@@ -54763,7 +54867,7 @@
         <v>87</v>
       </c>
       <c r="Z649" s="1" t="s">
-        <v>1838</v>
+        <v>1844</v>
       </c>
       <c r="AA649" s="1" t="s">
         <v>35</v>
@@ -54777,7 +54881,7 @@
         <v>28</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>1839</v>
+        <v>1845</v>
       </c>
       <c r="C650" s="1" t="s">
         <v>1241</v>
@@ -54786,11 +54890,13 @@
         <v>178</v>
       </c>
       <c r="E650" s="1" t="s">
-        <v>1820</v>
-      </c>
-      <c r="F650" s="1"/>
+        <v>1825</v>
+      </c>
+      <c r="F650" s="1" t="s">
+        <v>1826</v>
+      </c>
       <c r="G650" s="1" t="s">
-        <v>1840</v>
+        <v>1846</v>
       </c>
       <c r="H650" s="1" t="s">
         <v>449</v>
@@ -54803,12 +54909,12 @@
         <v>75</v>
       </c>
       <c r="L650" s="1" t="s">
-        <v>1841</v>
+        <v>1847</v>
       </c>
       <c r="M650" s="1"/>
       <c r="N650" s="1"/>
       <c r="O650" s="1" t="s">
-        <v>1842</v>
+        <v>1848</v>
       </c>
       <c r="P650" s="1"/>
       <c r="Q650" s="1" t="s">
@@ -54837,7 +54943,7 @@
         <v>317</v>
       </c>
       <c r="Z650" s="1" t="s">
-        <v>1821</v>
+        <v>1827</v>
       </c>
       <c r="AA650" s="1" t="s">
         <v>51</v>
@@ -54851,7 +54957,7 @@
         <v>28</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>1843</v>
+        <v>1849</v>
       </c>
       <c r="C651" s="1" t="s">
         <v>1241</v>
@@ -54860,11 +54966,13 @@
         <v>31</v>
       </c>
       <c r="E651" s="1" t="s">
-        <v>1844</v>
-      </c>
-      <c r="F651" s="1"/>
+        <v>1850</v>
+      </c>
+      <c r="F651" s="1" t="s">
+        <v>1851</v>
+      </c>
       <c r="G651" s="1" t="s">
-        <v>1845</v>
+        <v>1852</v>
       </c>
       <c r="H651" s="1" t="s">
         <v>153</v>
@@ -54874,7 +54982,7 @@
       </c>
       <c r="J651" s="1"/>
       <c r="K651" s="1" t="s">
-        <v>1846</v>
+        <v>1853</v>
       </c>
       <c r="L651" s="1" t="s">
         <v>774</v>
@@ -54911,7 +55019,7 @@
         <v>87</v>
       </c>
       <c r="Z651" s="1" t="s">
-        <v>1847</v>
+        <v>1854</v>
       </c>
       <c r="AA651" s="1" t="s">
         <v>51</v>
@@ -54925,7 +55033,7 @@
         <v>28</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>1848</v>
+        <v>1855</v>
       </c>
       <c r="C652" s="1" t="s">
         <v>1241</v>
@@ -54934,11 +55042,13 @@
         <v>31</v>
       </c>
       <c r="E652" s="1" t="s">
-        <v>1844</v>
-      </c>
-      <c r="F652" s="1"/>
+        <v>1850</v>
+      </c>
+      <c r="F652" s="1" t="s">
+        <v>1851</v>
+      </c>
       <c r="G652" s="1" t="s">
-        <v>1849</v>
+        <v>1856</v>
       </c>
       <c r="H652" s="1" t="s">
         <v>178</v>
@@ -54985,7 +55095,7 @@
         <v>123</v>
       </c>
       <c r="Z652" s="1" t="s">
-        <v>1847</v>
+        <v>1854</v>
       </c>
       <c r="AA652" s="1" t="s">
         <v>35</v>
@@ -54999,7 +55109,7 @@
         <v>28</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>1850</v>
+        <v>1857</v>
       </c>
       <c r="C653" s="1" t="s">
         <v>1241</v>
@@ -55008,9 +55118,11 @@
         <v>178</v>
       </c>
       <c r="E653" s="1" t="s">
-        <v>1844</v>
-      </c>
-      <c r="F653" s="1"/>
+        <v>1850</v>
+      </c>
+      <c r="F653" s="1" t="s">
+        <v>1851</v>
+      </c>
       <c r="G653" s="1" t="s">
         <v>1333</v>
       </c>
@@ -55022,7 +55134,7 @@
       </c>
       <c r="J653" s="1"/>
       <c r="K653" s="1" t="s">
-        <v>1851</v>
+        <v>1858</v>
       </c>
       <c r="L653" s="1" t="s">
         <v>738</v>
@@ -55059,7 +55171,7 @@
         <v>194</v>
       </c>
       <c r="Z653" s="1" t="s">
-        <v>1852</v>
+        <v>1859</v>
       </c>
       <c r="AA653" s="1" t="s">
         <v>154</v>
@@ -55073,7 +55185,7 @@
         <v>28</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>1853</v>
+        <v>1860</v>
       </c>
       <c r="C654" s="1" t="s">
         <v>1241</v>
@@ -55082,11 +55194,13 @@
         <v>31</v>
       </c>
       <c r="E654" s="1" t="s">
-        <v>1844</v>
-      </c>
-      <c r="F654" s="1"/>
+        <v>1850</v>
+      </c>
+      <c r="F654" s="1" t="s">
+        <v>1851</v>
+      </c>
       <c r="G654" s="1" t="s">
-        <v>1813</v>
+        <v>1818</v>
       </c>
       <c r="H654" s="1" t="s">
         <v>134</v>
@@ -55133,7 +55247,7 @@
         <v>135</v>
       </c>
       <c r="Z654" s="1" t="s">
-        <v>1847</v>
+        <v>1854</v>
       </c>
       <c r="AA654" s="1" t="s">
         <v>35</v>
@@ -55147,7 +55261,7 @@
         <v>28</v>
       </c>
       <c r="B655" s="1" t="s">
-        <v>1854</v>
+        <v>1861</v>
       </c>
       <c r="C655" s="1" t="s">
         <v>1241</v>
@@ -55156,11 +55270,13 @@
         <v>31</v>
       </c>
       <c r="E655" s="1" t="s">
-        <v>1844</v>
-      </c>
-      <c r="F655" s="1"/>
+        <v>1850</v>
+      </c>
+      <c r="F655" s="1" t="s">
+        <v>1851</v>
+      </c>
       <c r="G655" s="1" t="s">
-        <v>1855</v>
+        <v>1862</v>
       </c>
       <c r="H655" s="1" t="s">
         <v>409</v>
@@ -55207,7 +55323,7 @@
         <v>170</v>
       </c>
       <c r="Z655" s="1" t="s">
-        <v>1847</v>
+        <v>1854</v>
       </c>
       <c r="AA655" s="1" t="s">
         <v>51</v>
@@ -55221,7 +55337,7 @@
         <v>28</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>1856</v>
+        <v>1863</v>
       </c>
       <c r="C656" s="1" t="s">
         <v>1241</v>
@@ -55230,9 +55346,11 @@
         <v>31</v>
       </c>
       <c r="E656" s="1" t="s">
-        <v>1857</v>
-      </c>
-      <c r="F656" s="1"/>
+        <v>1864</v>
+      </c>
+      <c r="F656" s="1" t="s">
+        <v>1865</v>
+      </c>
       <c r="G656" s="1" t="s">
         <v>353</v>
       </c>
@@ -55281,7 +55399,7 @@
         <v>55</v>
       </c>
       <c r="Z656" s="1" t="s">
-        <v>1858</v>
+        <v>1866</v>
       </c>
       <c r="AA656" s="1" t="s">
         <v>51</v>
@@ -55295,7 +55413,7 @@
         <v>28</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>1859</v>
+        <v>1867</v>
       </c>
       <c r="C657" s="1" t="s">
         <v>1241</v>
@@ -55304,11 +55422,13 @@
         <v>31</v>
       </c>
       <c r="E657" s="1" t="s">
-        <v>1857</v>
-      </c>
-      <c r="F657" s="1"/>
+        <v>1864</v>
+      </c>
+      <c r="F657" s="1" t="s">
+        <v>1865</v>
+      </c>
       <c r="G657" s="1" t="s">
-        <v>1860</v>
+        <v>1868</v>
       </c>
       <c r="H657" s="1" t="s">
         <v>134</v>
@@ -55355,7 +55475,7 @@
         <v>135</v>
       </c>
       <c r="Z657" s="1" t="s">
-        <v>1858</v>
+        <v>1866</v>
       </c>
       <c r="AA657" s="1" t="s">
         <v>35</v>
@@ -55369,7 +55489,7 @@
         <v>28</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1861</v>
+        <v>1869</v>
       </c>
       <c r="C658" s="1" t="s">
         <v>1241</v>
@@ -55378,11 +55498,13 @@
         <v>31</v>
       </c>
       <c r="E658" s="1" t="s">
-        <v>1857</v>
-      </c>
-      <c r="F658" s="1"/>
+        <v>1864</v>
+      </c>
+      <c r="F658" s="1" t="s">
+        <v>1865</v>
+      </c>
       <c r="G658" s="1" t="s">
-        <v>1862</v>
+        <v>1870</v>
       </c>
       <c r="H658" s="1" t="s">
         <v>455</v>
@@ -55392,7 +55514,7 @@
       </c>
       <c r="J658" s="1"/>
       <c r="K658" s="1" t="s">
-        <v>1863</v>
+        <v>1871</v>
       </c>
       <c r="L658" s="1" t="s">
         <v>1494</v>
@@ -55429,7 +55551,7 @@
         <v>410</v>
       </c>
       <c r="Z658" s="1" t="s">
-        <v>1858</v>
+        <v>1866</v>
       </c>
       <c r="AA658" s="1" t="s">
         <v>35</v>
@@ -55443,7 +55565,7 @@
         <v>28</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="C659" s="1" t="s">
         <v>1241</v>
@@ -55452,9 +55574,11 @@
         <v>31</v>
       </c>
       <c r="E659" s="1" t="s">
-        <v>1857</v>
-      </c>
-      <c r="F659" s="1"/>
+        <v>1864</v>
+      </c>
+      <c r="F659" s="1" t="s">
+        <v>1865</v>
+      </c>
       <c r="G659" s="1" t="s">
         <v>109</v>
       </c>
@@ -55503,7 +55627,7 @@
         <v>70</v>
       </c>
       <c r="Z659" s="1" t="s">
-        <v>1858</v>
+        <v>1866</v>
       </c>
       <c r="AA659" s="1" t="s">
         <v>35</v>
@@ -55517,7 +55641,7 @@
         <v>28</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1865</v>
+        <v>1873</v>
       </c>
       <c r="C660" s="1" t="s">
         <v>1241</v>
@@ -55526,11 +55650,13 @@
         <v>31</v>
       </c>
       <c r="E660" s="1" t="s">
-        <v>1857</v>
-      </c>
-      <c r="F660" s="1"/>
+        <v>1864</v>
+      </c>
+      <c r="F660" s="1" t="s">
+        <v>1865</v>
+      </c>
       <c r="G660" s="1" t="s">
-        <v>1866</v>
+        <v>1874</v>
       </c>
       <c r="H660" s="1" t="s">
         <v>455</v>
@@ -55543,12 +55669,12 @@
         <v>75</v>
       </c>
       <c r="L660" s="1" t="s">
-        <v>1867</v>
+        <v>1875</v>
       </c>
       <c r="M660" s="1"/>
       <c r="N660" s="1"/>
       <c r="O660" s="1" t="s">
-        <v>1868</v>
+        <v>1876</v>
       </c>
       <c r="P660" s="1"/>
       <c r="Q660" s="1" t="s">
@@ -55577,7 +55703,7 @@
         <v>410</v>
       </c>
       <c r="Z660" s="1" t="s">
-        <v>1858</v>
+        <v>1866</v>
       </c>
       <c r="AA660" s="1" t="s">
         <v>51</v>
@@ -55591,7 +55717,7 @@
         <v>28</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1869</v>
+        <v>1877</v>
       </c>
       <c r="C661" s="1" t="s">
         <v>1241</v>
@@ -55600,9 +55726,11 @@
         <v>31</v>
       </c>
       <c r="E661" s="1" t="s">
-        <v>1857</v>
-      </c>
-      <c r="F661" s="1"/>
+        <v>1864</v>
+      </c>
+      <c r="F661" s="1" t="s">
+        <v>1865</v>
+      </c>
       <c r="G661" s="1" t="s">
         <v>1333</v>
       </c>
@@ -55651,7 +55779,7 @@
         <v>184</v>
       </c>
       <c r="Z661" s="1" t="s">
-        <v>1858</v>
+        <v>1866</v>
       </c>
       <c r="AA661" s="1" t="s">
         <v>35</v>
@@ -55665,7 +55793,7 @@
         <v>28</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1870</v>
+        <v>1878</v>
       </c>
       <c r="C662" s="1" t="s">
         <v>1241</v>
@@ -55674,9 +55802,11 @@
         <v>31</v>
       </c>
       <c r="E662" s="1" t="s">
-        <v>1857</v>
-      </c>
-      <c r="F662" s="1"/>
+        <v>1864</v>
+      </c>
+      <c r="F662" s="1" t="s">
+        <v>1865</v>
+      </c>
       <c r="G662" s="1" t="s">
         <v>1735</v>
       </c>
@@ -55725,7 +55855,7 @@
         <v>123</v>
       </c>
       <c r="Z662" s="1" t="s">
-        <v>1858</v>
+        <v>1866</v>
       </c>
       <c r="AA662" s="1" t="s">
         <v>35</v>
@@ -55739,7 +55869,7 @@
         <v>28</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1871</v>
+        <v>1879</v>
       </c>
       <c r="C663" s="1" t="s">
         <v>1241</v>
@@ -55748,11 +55878,13 @@
         <v>31</v>
       </c>
       <c r="E663" s="1" t="s">
-        <v>1857</v>
-      </c>
-      <c r="F663" s="1"/>
+        <v>1864</v>
+      </c>
+      <c r="F663" s="1" t="s">
+        <v>1865</v>
+      </c>
       <c r="G663" s="1" t="s">
-        <v>1872</v>
+        <v>1880</v>
       </c>
       <c r="H663" s="1" t="s">
         <v>372</v>
@@ -55799,7 +55931,7 @@
         <v>372</v>
       </c>
       <c r="Z663" s="1" t="s">
-        <v>1858</v>
+        <v>1866</v>
       </c>
       <c r="AA663" s="1" t="s">
         <v>35</v>
@@ -55813,7 +55945,7 @@
         <v>28</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1873</v>
+        <v>1881</v>
       </c>
       <c r="C664" s="1" t="s">
         <v>1241</v>
@@ -55824,9 +55956,11 @@
       <c r="E664" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="F664" s="1"/>
+      <c r="F664" s="1" t="s">
+        <v>1882</v>
+      </c>
       <c r="G664" s="1" t="s">
-        <v>1874</v>
+        <v>1883</v>
       </c>
       <c r="H664" s="1" t="s">
         <v>1269</v>
@@ -55873,7 +56007,7 @@
         <v>465</v>
       </c>
       <c r="Z664" s="1" t="s">
-        <v>1875</v>
+        <v>1884</v>
       </c>
       <c r="AA664" s="1" t="s">
         <v>51</v>
@@ -55887,7 +56021,7 @@
         <v>28</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1876</v>
+        <v>1885</v>
       </c>
       <c r="C665" s="1" t="s">
         <v>1241</v>
@@ -55898,7 +56032,9 @@
       <c r="E665" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="F665" s="1"/>
+      <c r="F665" s="1" t="s">
+        <v>1882</v>
+      </c>
       <c r="G665" s="1" t="s">
         <v>168</v>
       </c>
@@ -55910,7 +56046,7 @@
       </c>
       <c r="J665" s="1"/>
       <c r="K665" s="1" t="s">
-        <v>1877</v>
+        <v>1886</v>
       </c>
       <c r="L665" s="1" t="s">
         <v>61</v>
@@ -55947,7 +56083,7 @@
         <v>138</v>
       </c>
       <c r="Z665" s="1" t="s">
-        <v>1875</v>
+        <v>1884</v>
       </c>
       <c r="AA665" s="1" t="s">
         <v>154</v>
@@ -55961,7 +56097,7 @@
         <v>28</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1878</v>
+        <v>1887</v>
       </c>
       <c r="C666" s="1" t="s">
         <v>1241</v>
@@ -55972,9 +56108,11 @@
       <c r="E666" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="F666" s="1"/>
+      <c r="F666" s="1" t="s">
+        <v>1882</v>
+      </c>
       <c r="G666" s="1" t="s">
-        <v>1879</v>
+        <v>1888</v>
       </c>
       <c r="H666" s="1" t="s">
         <v>327</v>
@@ -55984,15 +56122,15 @@
       </c>
       <c r="J666" s="1"/>
       <c r="K666" s="1" t="s">
-        <v>1880</v>
+        <v>1889</v>
       </c>
       <c r="L666" s="1" t="s">
-        <v>1881</v>
+        <v>1890</v>
       </c>
       <c r="M666" s="1"/>
       <c r="N666" s="1"/>
       <c r="O666" s="1" t="s">
-        <v>1882</v>
+        <v>1891</v>
       </c>
       <c r="P666" s="1"/>
       <c r="Q666" s="1" t="s">
@@ -56021,7 +56159,7 @@
         <v>194</v>
       </c>
       <c r="Z666" s="1" t="s">
-        <v>1875</v>
+        <v>1884</v>
       </c>
       <c r="AA666" s="1" t="s">
         <v>51</v>
@@ -56035,7 +56173,7 @@
         <v>28</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1883</v>
+        <v>1892</v>
       </c>
       <c r="C667" s="1" t="s">
         <v>1241</v>
@@ -56046,9 +56184,11 @@
       <c r="E667" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="F667" s="1"/>
+      <c r="F667" s="1" t="s">
+        <v>1882</v>
+      </c>
       <c r="G667" s="1" t="s">
-        <v>1884</v>
+        <v>1893</v>
       </c>
       <c r="H667" s="1" t="s">
         <v>358</v>
@@ -56095,7 +56235,7 @@
         <v>71</v>
       </c>
       <c r="Z667" s="1" t="s">
-        <v>1875</v>
+        <v>1884</v>
       </c>
       <c r="AA667" s="1" t="s">
         <v>35</v>
@@ -56109,7 +56249,7 @@
         <v>28</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1885</v>
+        <v>1894</v>
       </c>
       <c r="C668" s="1" t="s">
         <v>1241</v>
@@ -56118,11 +56258,13 @@
         <v>31</v>
       </c>
       <c r="E668" s="1" t="s">
-        <v>1886</v>
-      </c>
-      <c r="F668" s="1"/>
+        <v>1895</v>
+      </c>
+      <c r="F668" s="1" t="s">
+        <v>1896</v>
+      </c>
       <c r="G668" s="1" t="s">
-        <v>1887</v>
+        <v>1897</v>
       </c>
       <c r="H668" s="1" t="s">
         <v>252</v>
@@ -56169,7 +56311,7 @@
         <v>253</v>
       </c>
       <c r="Z668" s="1" t="s">
-        <v>1888</v>
+        <v>1898</v>
       </c>
       <c r="AA668" s="1" t="s">
         <v>35</v>
@@ -56183,7 +56325,7 @@
         <v>28</v>
       </c>
       <c r="B669" s="1" t="s">
-        <v>1889</v>
+        <v>1899</v>
       </c>
       <c r="C669" s="1" t="s">
         <v>1241</v>
@@ -56192,11 +56334,13 @@
         <v>31</v>
       </c>
       <c r="E669" s="1" t="s">
-        <v>1886</v>
-      </c>
-      <c r="F669" s="1"/>
+        <v>1895</v>
+      </c>
+      <c r="F669" s="1" t="s">
+        <v>1896</v>
+      </c>
       <c r="G669" s="1" t="s">
-        <v>1890</v>
+        <v>1900</v>
       </c>
       <c r="H669" s="1" t="s">
         <v>275</v>
@@ -56243,7 +56387,7 @@
         <v>278</v>
       </c>
       <c r="Z669" s="1" t="s">
-        <v>1888</v>
+        <v>1898</v>
       </c>
       <c r="AA669" s="1" t="s">
         <v>51</v>
@@ -56257,7 +56401,7 @@
         <v>28</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1891</v>
+        <v>1901</v>
       </c>
       <c r="C670" s="1" t="s">
         <v>1241</v>
@@ -56266,11 +56410,13 @@
         <v>31</v>
       </c>
       <c r="E670" s="1" t="s">
-        <v>1886</v>
-      </c>
-      <c r="F670" s="1"/>
+        <v>1895</v>
+      </c>
+      <c r="F670" s="1" t="s">
+        <v>1896</v>
+      </c>
       <c r="G670" s="1" t="s">
-        <v>1892</v>
+        <v>1902</v>
       </c>
       <c r="H670" s="1" t="s">
         <v>142</v>
@@ -56317,7 +56463,7 @@
         <v>92</v>
       </c>
       <c r="Z670" s="1" t="s">
-        <v>1888</v>
+        <v>1898</v>
       </c>
       <c r="AA670" s="1" t="s">
         <v>35</v>
@@ -56331,7 +56477,7 @@
         <v>28</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1893</v>
+        <v>1903</v>
       </c>
       <c r="C671" s="1" t="s">
         <v>1241</v>
@@ -56340,11 +56486,13 @@
         <v>31</v>
       </c>
       <c r="E671" s="1" t="s">
-        <v>1886</v>
-      </c>
-      <c r="F671" s="1"/>
+        <v>1895</v>
+      </c>
+      <c r="F671" s="1" t="s">
+        <v>1896</v>
+      </c>
       <c r="G671" s="1" t="s">
-        <v>1894</v>
+        <v>1904</v>
       </c>
       <c r="H671" s="1" t="s">
         <v>182</v>
@@ -56391,7 +56539,7 @@
         <v>118</v>
       </c>
       <c r="Z671" s="1" t="s">
-        <v>1888</v>
+        <v>1898</v>
       </c>
       <c r="AA671" s="1" t="s">
         <v>35</v>
@@ -56405,7 +56553,7 @@
         <v>28</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1895</v>
+        <v>1905</v>
       </c>
       <c r="C672" s="1" t="s">
         <v>1241</v>
@@ -56414,11 +56562,13 @@
         <v>31</v>
       </c>
       <c r="E672" s="1" t="s">
-        <v>1886</v>
-      </c>
-      <c r="F672" s="1"/>
+        <v>1895</v>
+      </c>
+      <c r="F672" s="1" t="s">
+        <v>1896</v>
+      </c>
       <c r="G672" s="1" t="s">
-        <v>1896</v>
+        <v>1906</v>
       </c>
       <c r="H672" s="1" t="s">
         <v>34</v>
@@ -56428,15 +56578,15 @@
       </c>
       <c r="J672" s="1"/>
       <c r="K672" s="1" t="s">
-        <v>1897</v>
+        <v>1907</v>
       </c>
       <c r="L672" s="1" t="s">
-        <v>1898</v>
+        <v>1908</v>
       </c>
       <c r="M672" s="1"/>
       <c r="N672" s="1"/>
       <c r="O672" s="1" t="s">
-        <v>1899</v>
+        <v>1909</v>
       </c>
       <c r="P672" s="1"/>
       <c r="Q672" s="1" t="s">
@@ -56465,7 +56615,7 @@
         <v>45</v>
       </c>
       <c r="Z672" s="1" t="s">
-        <v>1888</v>
+        <v>1898</v>
       </c>
       <c r="AA672" s="1" t="s">
         <v>51</v>
@@ -56479,7 +56629,7 @@
         <v>28</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="C673" s="1" t="s">
         <v>1241</v>
@@ -56490,9 +56640,11 @@
       <c r="E673" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="F673" s="1"/>
+      <c r="F673" s="1" t="s">
+        <v>1911</v>
+      </c>
       <c r="G673" s="1" t="s">
-        <v>1901</v>
+        <v>1912</v>
       </c>
       <c r="H673" s="1" t="s">
         <v>216</v>
@@ -56539,7 +56691,7 @@
         <v>219</v>
       </c>
       <c r="Z673" s="1" t="s">
-        <v>1902</v>
+        <v>1913</v>
       </c>
       <c r="AA673" s="1" t="s">
         <v>35</v>
@@ -56553,7 +56705,7 @@
         <v>28</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1903</v>
+        <v>1914</v>
       </c>
       <c r="C674" s="1" t="s">
         <v>1241</v>
@@ -56564,7 +56716,9 @@
       <c r="E674" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="F674" s="1"/>
+      <c r="F674" s="1" t="s">
+        <v>1911</v>
+      </c>
       <c r="G674" s="1" t="s">
         <v>1434</v>
       </c>
@@ -56576,7 +56730,7 @@
       </c>
       <c r="J674" s="1"/>
       <c r="K674" s="1" t="s">
-        <v>1904</v>
+        <v>1915</v>
       </c>
       <c r="L674" s="1" t="s">
         <v>148</v>
@@ -56613,7 +56767,7 @@
         <v>111</v>
       </c>
       <c r="Z674" s="1" t="s">
-        <v>1902</v>
+        <v>1913</v>
       </c>
       <c r="AA674" s="1" t="s">
         <v>51</v>
@@ -56627,7 +56781,7 @@
         <v>28</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1905</v>
+        <v>1916</v>
       </c>
       <c r="C675" s="1" t="s">
         <v>1241</v>
@@ -56638,9 +56792,11 @@
       <c r="E675" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="F675" s="1"/>
+      <c r="F675" s="1" t="s">
+        <v>1911</v>
+      </c>
       <c r="G675" s="1" t="s">
-        <v>1906</v>
+        <v>1917</v>
       </c>
       <c r="H675" s="1" t="s">
         <v>285</v>
@@ -56687,7 +56843,7 @@
         <v>286</v>
       </c>
       <c r="Z675" s="1" t="s">
-        <v>1902</v>
+        <v>1913</v>
       </c>
       <c r="AA675" s="1" t="s">
         <v>51</v>
@@ -56701,7 +56857,7 @@
         <v>28</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1907</v>
+        <v>1918</v>
       </c>
       <c r="C676" s="1" t="s">
         <v>1241</v>
@@ -56712,9 +56868,11 @@
       <c r="E676" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="F676" s="1"/>
+      <c r="F676" s="1" t="s">
+        <v>1911</v>
+      </c>
       <c r="G676" s="1" t="s">
-        <v>1908</v>
+        <v>1919</v>
       </c>
       <c r="H676" s="1" t="s">
         <v>116</v>
@@ -56761,7 +56919,7 @@
         <v>105</v>
       </c>
       <c r="Z676" s="1" t="s">
-        <v>1902</v>
+        <v>1913</v>
       </c>
       <c r="AA676" s="1" t="s">
         <v>35</v>
@@ -56775,7 +56933,7 @@
         <v>28</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>1909</v>
+        <v>1920</v>
       </c>
       <c r="C677" s="1" t="s">
         <v>1241</v>
@@ -56784,11 +56942,13 @@
         <v>31</v>
       </c>
       <c r="E677" s="1" t="s">
-        <v>1910</v>
-      </c>
-      <c r="F677" s="1"/>
+        <v>1921</v>
+      </c>
+      <c r="F677" s="1" t="s">
+        <v>1922</v>
+      </c>
       <c r="G677" s="1" t="s">
-        <v>1911</v>
+        <v>1923</v>
       </c>
       <c r="H677" s="1" t="s">
         <v>121</v>
@@ -56835,7 +56995,7 @@
         <v>122</v>
       </c>
       <c r="Z677" s="1" t="s">
-        <v>1912</v>
+        <v>1924</v>
       </c>
       <c r="AA677" s="1" t="s">
         <v>35</v>
@@ -56849,7 +57009,7 @@
         <v>28</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>1913</v>
+        <v>1925</v>
       </c>
       <c r="C678" s="1" t="s">
         <v>1241</v>
@@ -56858,9 +57018,11 @@
         <v>31</v>
       </c>
       <c r="E678" s="1" t="s">
-        <v>1910</v>
-      </c>
-      <c r="F678" s="1"/>
+        <v>1921</v>
+      </c>
+      <c r="F678" s="1" t="s">
+        <v>1922</v>
+      </c>
       <c r="G678" s="1" t="s">
         <v>1468</v>
       </c>
@@ -56909,7 +57071,7 @@
         <v>56</v>
       </c>
       <c r="Z678" s="1" t="s">
-        <v>1912</v>
+        <v>1924</v>
       </c>
       <c r="AA678" s="1" t="s">
         <v>51</v>
@@ -56923,7 +57085,7 @@
         <v>28</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>1914</v>
+        <v>1926</v>
       </c>
       <c r="C679" s="1" t="s">
         <v>1241</v>
@@ -56932,9 +57094,11 @@
         <v>31</v>
       </c>
       <c r="E679" s="1" t="s">
-        <v>1910</v>
-      </c>
-      <c r="F679" s="1"/>
+        <v>1921</v>
+      </c>
+      <c r="F679" s="1" t="s">
+        <v>1922</v>
+      </c>
       <c r="G679" s="1" t="s">
         <v>539</v>
       </c>
@@ -56983,7 +57147,7 @@
         <v>179</v>
       </c>
       <c r="Z679" s="1" t="s">
-        <v>1912</v>
+        <v>1924</v>
       </c>
       <c r="AA679" s="1" t="s">
         <v>35</v>
@@ -56997,7 +57161,7 @@
         <v>28</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>1915</v>
+        <v>1927</v>
       </c>
       <c r="C680" s="1" t="s">
         <v>1241</v>
@@ -57006,11 +57170,13 @@
         <v>31</v>
       </c>
       <c r="E680" s="1" t="s">
-        <v>1910</v>
-      </c>
-      <c r="F680" s="1"/>
+        <v>1921</v>
+      </c>
+      <c r="F680" s="1" t="s">
+        <v>1922</v>
+      </c>
       <c r="G680" s="1" t="s">
-        <v>1916</v>
+        <v>1928</v>
       </c>
       <c r="H680" s="1" t="s">
         <v>336</v>
@@ -57020,10 +57186,10 @@
       </c>
       <c r="J680" s="1"/>
       <c r="K680" s="1" t="s">
-        <v>1917</v>
+        <v>1929</v>
       </c>
       <c r="L680" s="1" t="s">
-        <v>1918</v>
+        <v>1930</v>
       </c>
       <c r="M680" s="1"/>
       <c r="N680" s="1"/>
@@ -57057,7 +57223,7 @@
         <v>56</v>
       </c>
       <c r="Z680" s="1" t="s">
-        <v>1912</v>
+        <v>1924</v>
       </c>
       <c r="AA680" s="1" t="s">
         <v>51</v>
@@ -57071,7 +57237,7 @@
         <v>28</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>1919</v>
+        <v>1931</v>
       </c>
       <c r="C681" s="1" t="s">
         <v>1241</v>
@@ -57080,11 +57246,13 @@
         <v>31</v>
       </c>
       <c r="E681" s="1" t="s">
-        <v>1920</v>
-      </c>
-      <c r="F681" s="1"/>
+        <v>1932</v>
+      </c>
+      <c r="F681" s="1" t="s">
+        <v>1933</v>
+      </c>
       <c r="G681" s="1" t="s">
-        <v>1921</v>
+        <v>1934</v>
       </c>
       <c r="H681" s="1" t="s">
         <v>95</v>
@@ -57131,7 +57299,7 @@
         <v>99</v>
       </c>
       <c r="Z681" s="1" t="s">
-        <v>1922</v>
+        <v>1935</v>
       </c>
       <c r="AA681" s="1" t="s">
         <v>35</v>
@@ -57145,7 +57313,7 @@
         <v>28</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1923</v>
+        <v>1936</v>
       </c>
       <c r="C682" s="1" t="s">
         <v>1241</v>
@@ -57154,11 +57322,13 @@
         <v>31</v>
       </c>
       <c r="E682" s="1" t="s">
-        <v>1920</v>
-      </c>
-      <c r="F682" s="1"/>
+        <v>1932</v>
+      </c>
+      <c r="F682" s="1" t="s">
+        <v>1933</v>
+      </c>
       <c r="G682" s="1" t="s">
-        <v>1924</v>
+        <v>1937</v>
       </c>
       <c r="H682" s="1" t="s">
         <v>275</v>
@@ -57171,12 +57341,12 @@
         <v>75</v>
       </c>
       <c r="L682" s="1" t="s">
-        <v>1925</v>
+        <v>1938</v>
       </c>
       <c r="M682" s="1"/>
       <c r="N682" s="1"/>
       <c r="O682" s="1" t="s">
-        <v>1926</v>
+        <v>1939</v>
       </c>
       <c r="P682" s="1"/>
       <c r="Q682" s="1" t="s">
@@ -57205,7 +57375,7 @@
         <v>278</v>
       </c>
       <c r="Z682" s="1" t="s">
-        <v>1922</v>
+        <v>1935</v>
       </c>
       <c r="AA682" s="1" t="s">
         <v>51</v>
@@ -57219,7 +57389,7 @@
         <v>28</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>1927</v>
+        <v>1940</v>
       </c>
       <c r="C683" s="1" t="s">
         <v>1241</v>
@@ -57228,11 +57398,13 @@
         <v>31</v>
       </c>
       <c r="E683" s="1" t="s">
-        <v>1920</v>
-      </c>
-      <c r="F683" s="1"/>
+        <v>1932</v>
+      </c>
+      <c r="F683" s="1" t="s">
+        <v>1933</v>
+      </c>
       <c r="G683" s="1" t="s">
-        <v>1928</v>
+        <v>1941</v>
       </c>
       <c r="H683" s="1" t="s">
         <v>90</v>
@@ -57279,7 +57451,7 @@
         <v>91</v>
       </c>
       <c r="Z683" s="1" t="s">
-        <v>1922</v>
+        <v>1935</v>
       </c>
       <c r="AA683" s="1" t="s">
         <v>35</v>
@@ -57293,7 +57465,7 @@
         <v>28</v>
       </c>
       <c r="B684" s="1" t="s">
-        <v>1929</v>
+        <v>1942</v>
       </c>
       <c r="C684" s="1" t="s">
         <v>1241</v>
@@ -57302,11 +57474,13 @@
         <v>31</v>
       </c>
       <c r="E684" s="1" t="s">
-        <v>1920</v>
-      </c>
-      <c r="F684" s="1"/>
+        <v>1932</v>
+      </c>
+      <c r="F684" s="1" t="s">
+        <v>1933</v>
+      </c>
       <c r="G684" s="1" t="s">
-        <v>1930</v>
+        <v>1943</v>
       </c>
       <c r="H684" s="1" t="s">
         <v>485</v>
@@ -57319,12 +57493,12 @@
         <v>1134</v>
       </c>
       <c r="L684" s="1" t="s">
-        <v>1931</v>
+        <v>1944</v>
       </c>
       <c r="M684" s="1"/>
       <c r="N684" s="1"/>
       <c r="O684" s="1" t="s">
-        <v>1932</v>
+        <v>1945</v>
       </c>
       <c r="P684" s="1"/>
       <c r="Q684" s="1" t="s">
@@ -57353,7 +57527,7 @@
         <v>112</v>
       </c>
       <c r="Z684" s="1" t="s">
-        <v>1922</v>
+        <v>1935</v>
       </c>
       <c r="AA684" s="1" t="s">
         <v>51</v>
@@ -57367,7 +57541,7 @@
         <v>28</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>1933</v>
+        <v>1946</v>
       </c>
       <c r="C685" s="1" t="s">
         <v>1241</v>
@@ -57376,9 +57550,11 @@
         <v>31</v>
       </c>
       <c r="E685" s="1" t="s">
-        <v>1920</v>
-      </c>
-      <c r="F685" s="1"/>
+        <v>1932</v>
+      </c>
+      <c r="F685" s="1" t="s">
+        <v>1933</v>
+      </c>
       <c r="G685" s="1" t="s">
         <v>914</v>
       </c>
@@ -57427,7 +57603,7 @@
         <v>272</v>
       </c>
       <c r="Z685" s="1" t="s">
-        <v>1922</v>
+        <v>1935</v>
       </c>
       <c r="AA685" s="1" t="s">
         <v>35</v>
@@ -57441,7 +57617,7 @@
         <v>28</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>1934</v>
+        <v>1947</v>
       </c>
       <c r="C686" s="1" t="s">
         <v>1241</v>
@@ -57450,11 +57626,13 @@
         <v>31</v>
       </c>
       <c r="E686" s="1" t="s">
-        <v>1920</v>
-      </c>
-      <c r="F686" s="1"/>
+        <v>1932</v>
+      </c>
+      <c r="F686" s="1" t="s">
+        <v>1933</v>
+      </c>
       <c r="G686" s="1" t="s">
-        <v>1935</v>
+        <v>1948</v>
       </c>
       <c r="H686" s="1" t="s">
         <v>64</v>
@@ -57467,7 +57645,7 @@
         <v>60</v>
       </c>
       <c r="L686" s="1" t="s">
-        <v>1936</v>
+        <v>1949</v>
       </c>
       <c r="M686" s="1"/>
       <c r="N686" s="1"/>
@@ -57501,7 +57679,7 @@
         <v>64</v>
       </c>
       <c r="Z686" s="1" t="s">
-        <v>1922</v>
+        <v>1935</v>
       </c>
       <c r="AA686" s="1" t="s">
         <v>35</v>
